--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasAcebo\OneDrive - LARTIRIGOYEN Y CIA. S.A\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F7CB77-BF62-4F35-B405-BE12BDF74260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C4691A-A7BA-447F-ADA6-5327F037706D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5F5C8F4A-A9C3-4394-B81C-80D194F2AEAA}"/>
   </bookViews>
@@ -2695,19 +2695,19 @@
         <v>16</v>
       </c>
       <c r="H57">
-        <v>1.9</v>
+        <v>0.19</v>
       </c>
       <c r="I57">
         <v>10.9</v>
       </c>
       <c r="J57">
-        <v>93.69863013698631</v>
+        <v>9.3698630136986303</v>
       </c>
       <c r="K57" s="2">
-        <v>214.81178082191781</v>
+        <v>121.29117808219178</v>
       </c>
       <c r="L57" s="2">
-        <v>2.3281277777777771</v>
+        <v>0.43173777777777783</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
